--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/108.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/108.xlsx
@@ -426,13 +426,13 @@
         <v>-40.14070621652547</v>
       </c>
       <c r="E2">
-        <v>-12.66409924954716</v>
+        <v>-12.79071404999588</v>
       </c>
       <c r="F2">
-        <v>0.1432436291467911</v>
+        <v>0.477938851308709</v>
       </c>
       <c r="G2">
-        <v>-19.89696827782692</v>
+        <v>-22.41759127102727</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-39.16334001345233</v>
       </c>
       <c r="E3">
-        <v>-12.81774314929786</v>
+        <v>-13.68387460503423</v>
       </c>
       <c r="F3">
-        <v>-0.7225229051543065</v>
+        <v>0.7093134640542501</v>
       </c>
       <c r="G3">
-        <v>-19.41105649452891</v>
+        <v>-21.80697857770704</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-37.87708246477274</v>
       </c>
       <c r="E4">
-        <v>-12.59074938433936</v>
+        <v>-14.61287322059453</v>
       </c>
       <c r="F4">
-        <v>-0.06389461012764201</v>
+        <v>0.3622208953420349</v>
       </c>
       <c r="G4">
-        <v>-18.24745676787579</v>
+        <v>-21.15328076639966</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-36.43848855959512</v>
       </c>
       <c r="E5">
-        <v>-13.64318974689621</v>
+        <v>-14.94277110254831</v>
       </c>
       <c r="F5">
-        <v>0.04640499465732055</v>
+        <v>0.7516099036411928</v>
       </c>
       <c r="G5">
-        <v>-17.93658888255046</v>
+        <v>-20.98361043348165</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-34.90097498145185</v>
       </c>
       <c r="E6">
-        <v>-14.67883452285546</v>
+        <v>-15.85102442754109</v>
       </c>
       <c r="F6">
-        <v>-0.6932508862415804</v>
+        <v>1.192432243980172</v>
       </c>
       <c r="G6">
-        <v>-17.42918022828922</v>
+        <v>-20.02991979344322</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-33.37147621369218</v>
       </c>
       <c r="E7">
-        <v>-15.33586424802068</v>
+        <v>-16.09532047087883</v>
       </c>
       <c r="F7">
-        <v>0.3684949500508383</v>
+        <v>0.5700267987431245</v>
       </c>
       <c r="G7">
-        <v>-16.64276260494801</v>
+        <v>-19.60990124556647</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-31.89452753525635</v>
       </c>
       <c r="E8">
-        <v>-15.04054600355742</v>
+        <v>-16.81025426833481</v>
       </c>
       <c r="F8">
-        <v>-0.2435989777561612</v>
+        <v>1.06652702569387</v>
       </c>
       <c r="G8">
-        <v>-16.28922079390863</v>
+        <v>-18.3770397702834</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-30.53449931147411</v>
       </c>
       <c r="E9">
-        <v>-15.76703818813041</v>
+        <v>-17.65875534199728</v>
       </c>
       <c r="F9">
-        <v>-0.3757799074860727</v>
+        <v>0.6561562994492031</v>
       </c>
       <c r="G9">
-        <v>-16.09867168380934</v>
+        <v>-17.78170384893807</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-29.30542531928161</v>
       </c>
       <c r="E10">
-        <v>-16.66671097852609</v>
+        <v>-18.74271857850959</v>
       </c>
       <c r="F10">
-        <v>0.573973969417464</v>
+        <v>1.030942018804408</v>
       </c>
       <c r="G10">
-        <v>-14.50472987248006</v>
+        <v>-16.94244344970043</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-28.21664100294388</v>
       </c>
       <c r="E11">
-        <v>-16.91380628629677</v>
+        <v>-19.20796131111688</v>
       </c>
       <c r="F11">
-        <v>-0.0594090006414827</v>
+        <v>1.242505396744597</v>
       </c>
       <c r="G11">
-        <v>-14.12793807548452</v>
+        <v>-16.15801129762076</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-27.27309486827533</v>
       </c>
       <c r="E12">
-        <v>-17.47915802467772</v>
+        <v>-19.57221455714964</v>
       </c>
       <c r="F12">
-        <v>0.4267979329620759</v>
+        <v>1.274909472807308</v>
       </c>
       <c r="G12">
-        <v>-14.16639825942851</v>
+        <v>-15.26705815547907</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-26.45224863408037</v>
       </c>
       <c r="E13">
-        <v>-19.2226179938822</v>
+        <v>-19.97178255907742</v>
       </c>
       <c r="F13">
-        <v>0.3092774495269101</v>
+        <v>1.361145832908347</v>
       </c>
       <c r="G13">
-        <v>-12.71641159948092</v>
+        <v>-14.83199976069907</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-25.76004657249871</v>
       </c>
       <c r="E14">
-        <v>-18.89357982667266</v>
+        <v>-21.84660860248622</v>
       </c>
       <c r="F14">
-        <v>0.8321537229501944</v>
+        <v>1.617084852616505</v>
       </c>
       <c r="G14">
-        <v>-11.97033911767847</v>
+        <v>-13.69111873347781</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-25.16490563743239</v>
       </c>
       <c r="E15">
-        <v>-20.28855214003342</v>
+        <v>-22.73078991464029</v>
       </c>
       <c r="F15">
-        <v>1.409683192507982</v>
+        <v>1.843189391945436</v>
       </c>
       <c r="G15">
-        <v>-12.30366723872116</v>
+        <v>-13.21421010290226</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-24.64208932449271</v>
       </c>
       <c r="E16">
-        <v>-22.2516297708835</v>
+        <v>-22.47594471453749</v>
       </c>
       <c r="F16">
-        <v>0.9649493012929832</v>
+        <v>1.854142065745251</v>
       </c>
       <c r="G16">
-        <v>-10.63502549777865</v>
+        <v>-12.79353691081929</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-24.15826747907844</v>
       </c>
       <c r="E17">
-        <v>-23.82335445180631</v>
+        <v>-23.82835491824141</v>
       </c>
       <c r="F17">
-        <v>1.581420322456375</v>
+        <v>2.326551711887781</v>
       </c>
       <c r="G17">
-        <v>-12.05128916984283</v>
+        <v>-12.24586404810162</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-23.67789102541885</v>
       </c>
       <c r="E18">
-        <v>-23.39429864947225</v>
+        <v>-24.65912593275819</v>
       </c>
       <c r="F18">
-        <v>2.184985379484151</v>
+        <v>2.410496807752677</v>
       </c>
       <c r="G18">
-        <v>-10.90879600783656</v>
+        <v>-12.50162172585314</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-23.18618376782701</v>
       </c>
       <c r="E19">
-        <v>-24.08032194289611</v>
+        <v>-25.9492753454916</v>
       </c>
       <c r="F19">
-        <v>1.58078247955622</v>
+        <v>2.647404914748919</v>
       </c>
       <c r="G19">
-        <v>-11.18844330396907</v>
+        <v>-11.76219750515197</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-22.65189229054208</v>
       </c>
       <c r="E20">
-        <v>-24.70389339762851</v>
+        <v>-26.38176170037997</v>
       </c>
       <c r="F20">
-        <v>1.666632820447555</v>
+        <v>2.773482433455004</v>
       </c>
       <c r="G20">
-        <v>-9.11882643888354</v>
+        <v>-11.91018364618234</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-22.06867250138972</v>
       </c>
       <c r="E21">
-        <v>-25.79402415295818</v>
+        <v>-27.34201738437093</v>
       </c>
       <c r="F21">
-        <v>1.249236710259745</v>
+        <v>2.893473108485318</v>
       </c>
       <c r="G21">
-        <v>-10.71032850939243</v>
+        <v>-11.14567800219434</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-21.42682424658087</v>
       </c>
       <c r="E22">
-        <v>-24.53626978855843</v>
+        <v>-27.44125006255506</v>
       </c>
       <c r="F22">
-        <v>1.808515589199054</v>
+        <v>2.957746135268531</v>
       </c>
       <c r="G22">
-        <v>-9.445981454340536</v>
+        <v>-10.88151894834861</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-20.73265347111998</v>
       </c>
       <c r="E23">
-        <v>-26.22683030511856</v>
+        <v>-28.41740008628613</v>
       </c>
       <c r="F23">
-        <v>1.722994938534033</v>
+        <v>3.002610513804153</v>
       </c>
       <c r="G23">
-        <v>-10.27360707030788</v>
+        <v>-11.41838332845908</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-20.00743587479423</v>
       </c>
       <c r="E24">
-        <v>-26.65157092088613</v>
+        <v>-27.1465340337339</v>
       </c>
       <c r="F24">
-        <v>2.205116364106984</v>
+        <v>2.905224328461431</v>
       </c>
       <c r="G24">
-        <v>-10.25165854053039</v>
+        <v>-11.07883380305577</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-19.26774612113644</v>
       </c>
       <c r="E25">
-        <v>-28.05953655587662</v>
+        <v>-28.37590119872845</v>
       </c>
       <c r="F25">
-        <v>2.615400111774357</v>
+        <v>3.060889474060709</v>
       </c>
       <c r="G25">
-        <v>-9.933423133968933</v>
+        <v>-10.99364781779233</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-18.55741594879061</v>
       </c>
       <c r="E26">
-        <v>-26.00983331981892</v>
+        <v>-28.3388919326129</v>
       </c>
       <c r="F26">
-        <v>1.901398769340157</v>
+        <v>2.711813793786192</v>
       </c>
       <c r="G26">
-        <v>-10.3081198084301</v>
+        <v>-11.58104054871921</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-17.90566499261207</v>
       </c>
       <c r="E27">
-        <v>-26.36846727092919</v>
+        <v>-28.41628910225674</v>
       </c>
       <c r="F27">
-        <v>1.973052549682314</v>
+        <v>2.544844746608312</v>
       </c>
       <c r="G27">
-        <v>-8.913144147761862</v>
+        <v>-11.23487278577743</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-17.35375030138069</v>
       </c>
       <c r="E28">
-        <v>-25.9698503543948</v>
+        <v>-27.56257782498727</v>
       </c>
       <c r="F28">
-        <v>1.422363840710037</v>
+        <v>2.301944229820219</v>
       </c>
       <c r="G28">
-        <v>-9.50269465909329</v>
+        <v>-10.86079877390124</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-16.93062520661579</v>
       </c>
       <c r="E29">
-        <v>-24.25205723117777</v>
+        <v>-28.24822525278623</v>
       </c>
       <c r="F29">
-        <v>1.209905825974825</v>
+        <v>2.095790091020311</v>
       </c>
       <c r="G29">
-        <v>-11.11373815286666</v>
+        <v>-10.62511511131078</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-16.66290892204701</v>
       </c>
       <c r="E30">
-        <v>-25.7246904431015</v>
+        <v>-27.36476867600834</v>
       </c>
       <c r="F30">
-        <v>1.899644287181028</v>
+        <v>2.118658001541994</v>
       </c>
       <c r="G30">
-        <v>-9.893513986776881</v>
+        <v>-10.22190257905318</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-16.57187858900988</v>
       </c>
       <c r="E31">
-        <v>-24.18521544811598</v>
+        <v>-26.65432865320582</v>
       </c>
       <c r="F31">
-        <v>1.501979888527903</v>
+        <v>2.02167605949184</v>
       </c>
       <c r="G31">
-        <v>-9.412335483422565</v>
+        <v>-10.44163198144734</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-16.65947762546679</v>
       </c>
       <c r="E32">
-        <v>-24.6710373428378</v>
+        <v>-26.95347200529924</v>
       </c>
       <c r="F32">
-        <v>1.991218646825707</v>
+        <v>1.660748098418067</v>
       </c>
       <c r="G32">
-        <v>-9.5131506911807</v>
+        <v>-11.01392547103151</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.93012115591468</v>
       </c>
       <c r="E33">
-        <v>-22.73934137675812</v>
+        <v>-26.14820170831691</v>
       </c>
       <c r="F33">
-        <v>1.671412500361708</v>
+        <v>1.832917636150722</v>
       </c>
       <c r="G33">
-        <v>-10.14155299814478</v>
+        <v>-10.68176565819335</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-17.36405752701289</v>
       </c>
       <c r="E34">
-        <v>-24.43211140174306</v>
+        <v>-24.83313718084585</v>
       </c>
       <c r="F34">
-        <v>1.074944895241118</v>
+        <v>2.230863679720799</v>
       </c>
       <c r="G34">
-        <v>-9.600523175039193</v>
+        <v>-10.05199793180812</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-17.94811631749284</v>
       </c>
       <c r="E35">
-        <v>-24.31454229555981</v>
+        <v>-25.31668726897299</v>
       </c>
       <c r="F35">
-        <v>1.271451867268023</v>
+        <v>1.713511788506784</v>
       </c>
       <c r="G35">
-        <v>-10.18598264959635</v>
+        <v>-10.14057396892311</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-18.65249636119956</v>
       </c>
       <c r="E36">
-        <v>-23.28764002943933</v>
+        <v>-24.39994062682094</v>
       </c>
       <c r="F36">
-        <v>1.440112440682419</v>
+        <v>1.943493087280817</v>
       </c>
       <c r="G36">
-        <v>-10.70073141227549</v>
+        <v>-10.98730501380822</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-19.44583975668951</v>
       </c>
       <c r="E37">
-        <v>-21.76000168672957</v>
+        <v>-23.36384730403861</v>
       </c>
       <c r="F37">
-        <v>1.597596681098244</v>
+        <v>2.440094375054704</v>
       </c>
       <c r="G37">
-        <v>-9.232670567523625</v>
+        <v>-11.10498824236954</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-20.3007051128174</v>
       </c>
       <c r="E38">
-        <v>-20.63748003627756</v>
+        <v>-22.89139459657141</v>
       </c>
       <c r="F38">
-        <v>1.372073655686079</v>
+        <v>2.196340639841726</v>
       </c>
       <c r="G38">
-        <v>-9.054086499885408</v>
+        <v>-10.58667450795123</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-21.17827593836459</v>
       </c>
       <c r="E39">
-        <v>-21.27106073030281</v>
+        <v>-22.69481479814463</v>
       </c>
       <c r="F39">
-        <v>1.507470307673658</v>
+        <v>2.233295766415418</v>
       </c>
       <c r="G39">
-        <v>-8.656355225896846</v>
+        <v>-10.66368103041071</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-22.05449546875652</v>
       </c>
       <c r="E40">
-        <v>-19.38065599121457</v>
+        <v>-22.56641827003756</v>
       </c>
       <c r="F40">
-        <v>1.953082268335624</v>
+        <v>2.433962799539182</v>
       </c>
       <c r="G40">
-        <v>-10.43179600120032</v>
+        <v>-10.7044008137983</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-22.89040697101456</v>
       </c>
       <c r="E41">
-        <v>-19.62949149453035</v>
+        <v>-21.68274780287643</v>
       </c>
       <c r="F41">
-        <v>1.589876296904153</v>
+        <v>2.183598692451865</v>
       </c>
       <c r="G41">
-        <v>-10.30916541163884</v>
+        <v>-11.63600585996821</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-23.66690800284105</v>
       </c>
       <c r="E42">
-        <v>-18.93888305580389</v>
+        <v>-21.292939847562</v>
       </c>
       <c r="F42">
-        <v>2.18632567794188</v>
+        <v>2.514549693953129</v>
       </c>
       <c r="G42">
-        <v>-10.2857940260592</v>
+        <v>-11.25836948709745</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-24.36148616031721</v>
       </c>
       <c r="E43">
-        <v>-18.288851491721</v>
+        <v>-19.66901760670875</v>
       </c>
       <c r="F43">
-        <v>2.050432005512622</v>
+        <v>2.655554393257661</v>
       </c>
       <c r="G43">
-        <v>-11.12057960906767</v>
+        <v>-11.4989313259564</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-24.95730160163607</v>
       </c>
       <c r="E44">
-        <v>-18.41990607507596</v>
+        <v>-20.60688332844755</v>
       </c>
       <c r="F44">
-        <v>2.322565607945509</v>
+        <v>2.511264388833626</v>
       </c>
       <c r="G44">
-        <v>-11.44969007222341</v>
+        <v>-11.72043342392793</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-25.45277953070098</v>
       </c>
       <c r="E45">
-        <v>-16.38995343547349</v>
+        <v>-19.54480336240577</v>
       </c>
       <c r="F45">
-        <v>1.634154191318592</v>
+        <v>2.728722429212135</v>
       </c>
       <c r="G45">
-        <v>-9.387972014898295</v>
+        <v>-11.66185875828171</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-25.8389526707995</v>
       </c>
       <c r="E46">
-        <v>-18.62811071200094</v>
+        <v>-18.39456317957186</v>
       </c>
       <c r="F46">
-        <v>1.635847374289914</v>
+        <v>2.982133271606949</v>
       </c>
       <c r="G46">
-        <v>-10.85942682761861</v>
+        <v>-12.54234411998533</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-26.131384209259</v>
       </c>
       <c r="E47">
-        <v>-16.65899015867323</v>
+        <v>-17.80240661530046</v>
       </c>
       <c r="F47">
-        <v>1.818822136424685</v>
+        <v>3.169690562214007</v>
       </c>
       <c r="G47">
-        <v>-11.40566639155576</v>
+        <v>-13.28503438216998</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-26.33828150436464</v>
       </c>
       <c r="E48">
-        <v>-16.18083509205705</v>
+        <v>-17.92127152341705</v>
       </c>
       <c r="F48">
-        <v>1.70369563478361</v>
+        <v>2.85027871863374</v>
       </c>
       <c r="G48">
-        <v>-12.00511945712129</v>
+        <v>-12.92539517713806</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-26.47326900046498</v>
       </c>
       <c r="E49">
-        <v>-15.03336925438812</v>
+        <v>-18.04131594354989</v>
       </c>
       <c r="F49">
-        <v>1.818330086187423</v>
+        <v>3.350143773974657</v>
       </c>
       <c r="G49">
-        <v>-11.29277126857455</v>
+        <v>-13.10739670944604</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-26.55694715109503</v>
       </c>
       <c r="E50">
-        <v>-14.22704404172928</v>
+        <v>-16.90279612307464</v>
       </c>
       <c r="F50">
-        <v>1.560964617811644</v>
+        <v>2.9949017267537</v>
       </c>
       <c r="G50">
-        <v>-12.41166852096633</v>
+        <v>-12.94221489916631</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-26.59649438396487</v>
       </c>
       <c r="E51">
-        <v>-15.18408929336615</v>
+        <v>-16.60627760053851</v>
       </c>
       <c r="F51">
-        <v>2.203935112190592</v>
+        <v>2.400740296482505</v>
       </c>
       <c r="G51">
-        <v>-12.22927929308657</v>
+        <v>-13.21459388235716</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-26.60933943917405</v>
       </c>
       <c r="E52">
-        <v>-15.70560803942487</v>
+        <v>-16.28854862776648</v>
       </c>
       <c r="F52">
-        <v>1.735006265874626</v>
+        <v>2.725173703258542</v>
       </c>
       <c r="G52">
-        <v>-12.07236440555459</v>
+        <v>-13.47846314355327</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-26.59736962871007</v>
       </c>
       <c r="E53">
-        <v>-13.03919237713772</v>
+        <v>-15.16687838563606</v>
       </c>
       <c r="F53">
-        <v>1.768111140760105</v>
+        <v>2.596826457868787</v>
       </c>
       <c r="G53">
-        <v>-12.62354741437502</v>
+        <v>-13.66275560423996</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-26.56631003267221</v>
       </c>
       <c r="E54">
-        <v>-12.72851555719525</v>
+        <v>-15.31167179205356</v>
       </c>
       <c r="F54">
-        <v>2.405886114788695</v>
+        <v>2.880088347990883</v>
       </c>
       <c r="G54">
-        <v>-12.32911416625074</v>
+        <v>-13.80510645307041</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-26.52335856152357</v>
       </c>
       <c r="E55">
-        <v>-12.96916923420111</v>
+        <v>-15.24715580733367</v>
       </c>
       <c r="F55">
-        <v>1.773180749265238</v>
+        <v>2.506660322808866</v>
       </c>
       <c r="G55">
-        <v>-12.19713972179767</v>
+        <v>-13.59153579716668</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-26.46315405146221</v>
       </c>
       <c r="E56">
-        <v>-13.38155404627731</v>
+        <v>-13.59246242377476</v>
       </c>
       <c r="F56">
-        <v>2.121814081346661</v>
+        <v>2.548010766821812</v>
       </c>
       <c r="G56">
-        <v>-12.60164718337247</v>
+        <v>-14.08700943252964</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-26.39092854327909</v>
       </c>
       <c r="E57">
-        <v>-12.10557539058421</v>
+        <v>-14.7334575581996</v>
       </c>
       <c r="F57">
-        <v>2.341190620630054</v>
+        <v>2.768268689021784</v>
       </c>
       <c r="G57">
-        <v>-12.50784313021376</v>
+        <v>-14.0933365720462</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-26.29618815802666</v>
       </c>
       <c r="E58">
-        <v>-13.15917865231202</v>
+        <v>-14.43556432271495</v>
       </c>
       <c r="F58">
-        <v>2.050819681457132</v>
+        <v>2.541786414157177</v>
       </c>
       <c r="G58">
-        <v>-12.98120506426229</v>
+        <v>-13.89093990299244</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-26.17794237944925</v>
       </c>
       <c r="E59">
-        <v>-12.82990790526829</v>
+        <v>-13.90740874495915</v>
       </c>
       <c r="F59">
-        <v>2.046275257885374</v>
+        <v>2.677801028227244</v>
       </c>
       <c r="G59">
-        <v>-13.37136126281974</v>
+        <v>-14.1510953800077</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-26.03281400010864</v>
       </c>
       <c r="E60">
-        <v>-12.14006781063691</v>
+        <v>-12.94779265551222</v>
       </c>
       <c r="F60">
-        <v>2.484451792739812</v>
+        <v>2.919785370667841</v>
       </c>
       <c r="G60">
-        <v>-14.32299855223726</v>
+        <v>-13.85754456355522</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-25.85003167360275</v>
       </c>
       <c r="E61">
-        <v>-11.75629447137746</v>
+        <v>-12.52034414596087</v>
       </c>
       <c r="F61">
-        <v>2.025907360185339</v>
+        <v>2.53101101098156</v>
       </c>
       <c r="G61">
-        <v>-13.4739021727526</v>
+        <v>-14.18438759503358</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-25.63579744321789</v>
       </c>
       <c r="E62">
-        <v>-12.77104028795017</v>
+        <v>-13.40387340393694</v>
       </c>
       <c r="F62">
-        <v>2.228207933827424</v>
+        <v>2.69627859151409</v>
       </c>
       <c r="G62">
-        <v>-13.44301445349513</v>
+        <v>-14.00885679319466</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-25.38180299720148</v>
       </c>
       <c r="E63">
-        <v>-10.80125106759916</v>
+        <v>-12.40753046674455</v>
       </c>
       <c r="F63">
-        <v>1.751282028604831</v>
+        <v>2.377751444320013</v>
       </c>
       <c r="G63">
-        <v>-12.88080104877725</v>
+        <v>-14.24734309010368</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-25.09048068341089</v>
       </c>
       <c r="E64">
-        <v>-10.64248210507361</v>
+        <v>-12.93385032509477</v>
       </c>
       <c r="F64">
-        <v>1.281746817350015</v>
+        <v>2.562734169039171</v>
       </c>
       <c r="G64">
-        <v>-12.89568490369119</v>
+        <v>-14.23564695433549</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-24.75958270960436</v>
       </c>
       <c r="E65">
-        <v>-10.61314797348635</v>
+        <v>-12.68656812281448</v>
       </c>
       <c r="F65">
-        <v>1.9286636540359</v>
+        <v>2.874298059845315</v>
       </c>
       <c r="G65">
-        <v>-13.25734743578123</v>
+        <v>-13.43755538655512</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-24.38602122144477</v>
       </c>
       <c r="E66">
-        <v>-10.03564393876894</v>
+        <v>-12.51624077317194</v>
       </c>
       <c r="F66">
-        <v>1.590709634511369</v>
+        <v>2.852944404935949</v>
       </c>
       <c r="G66">
-        <v>-13.48680969401106</v>
+        <v>-13.48719347346595</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-23.98235708920286</v>
       </c>
       <c r="E67">
-        <v>-11.64579828408039</v>
+        <v>-13.17934249329406</v>
       </c>
       <c r="F67">
-        <v>1.410866101159179</v>
+        <v>2.427017767234111</v>
       </c>
       <c r="G67">
-        <v>-13.71557618880736</v>
+        <v>-13.12987391500323</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-23.54989825119365</v>
       </c>
       <c r="E68">
-        <v>-9.341280997004832</v>
+        <v>-12.54522603500791</v>
       </c>
       <c r="F68">
-        <v>1.658103949668331</v>
+        <v>2.578711719504367</v>
       </c>
       <c r="G68">
-        <v>-13.15324530058288</v>
+        <v>-13.794120439831</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-23.10709915394689</v>
       </c>
       <c r="E69">
-        <v>-10.1154271283189</v>
+        <v>-12.75315655998545</v>
       </c>
       <c r="F69">
-        <v>1.749380097048003</v>
+        <v>2.745135700931205</v>
       </c>
       <c r="G69">
-        <v>-11.86588453196033</v>
+        <v>-13.52435089585897</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-22.66337098764976</v>
       </c>
       <c r="E70">
-        <v>-11.68993446082935</v>
+        <v>-13.04538481522304</v>
       </c>
       <c r="F70">
-        <v>2.062695156543666</v>
+        <v>2.267338353200867</v>
       </c>
       <c r="G70">
-        <v>-11.9583740752174</v>
+        <v>-12.64984283389671</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-22.2351196921444</v>
       </c>
       <c r="E71">
-        <v>-12.32731534321681</v>
+        <v>-13.08582878710422</v>
       </c>
       <c r="F71">
-        <v>1.998213381174947</v>
+        <v>2.443664638560769</v>
       </c>
       <c r="G71">
-        <v>-12.27755326594855</v>
+        <v>-12.79483314550878</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-21.83869015018454</v>
       </c>
       <c r="E72">
-        <v>-10.43939422450082</v>
+        <v>-13.17187917254334</v>
       </c>
       <c r="F72">
-        <v>1.672878710664663</v>
+        <v>2.349853686928531</v>
       </c>
       <c r="G72">
-        <v>-12.20957208754055</v>
+        <v>-12.21886503291262</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-21.47532189856104</v>
       </c>
       <c r="E73">
-        <v>-11.85032317577158</v>
+        <v>-13.15506697310044</v>
       </c>
       <c r="F73">
-        <v>1.273903834780309</v>
+        <v>2.244989000673336</v>
       </c>
       <c r="G73">
-        <v>-14.06497213743605</v>
+        <v>-12.26870545252927</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-21.15813401146259</v>
       </c>
       <c r="E74">
-        <v>-12.1530133703364</v>
+        <v>-13.8892342922017</v>
       </c>
       <c r="F74">
-        <v>1.669290223075736</v>
+        <v>2.138928151888499</v>
       </c>
       <c r="G74">
-        <v>-11.5688509822233</v>
+        <v>-11.87570093162291</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-20.88183479336563</v>
       </c>
       <c r="E75">
-        <v>-12.07585085713242</v>
+        <v>-14.07202542903006</v>
       </c>
       <c r="F75">
-        <v>1.922783902210829</v>
+        <v>2.06608152248631</v>
       </c>
       <c r="G75">
-        <v>-12.51292102844348</v>
+        <v>-11.6615389420693</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-20.64461831032947</v>
       </c>
       <c r="E76">
-        <v>-11.22479555850517</v>
+        <v>-13.85183877743295</v>
       </c>
       <c r="F76">
-        <v>2.169523073543496</v>
+        <v>2.037469712393615</v>
       </c>
       <c r="G76">
-        <v>-11.6552522690939</v>
+        <v>-11.07995511785765</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-20.43710492884249</v>
       </c>
       <c r="E77">
-        <v>-11.28395390061603</v>
+        <v>-13.78623465134596</v>
       </c>
       <c r="F77">
-        <v>1.572024979373823</v>
+        <v>1.633362272081516</v>
       </c>
       <c r="G77">
-        <v>-11.23352564156841</v>
+        <v>-11.33897753172037</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-20.24328396447119</v>
       </c>
       <c r="E78">
-        <v>-14.22023692836789</v>
+        <v>-14.66274082897175</v>
       </c>
       <c r="F78">
-        <v>1.917611576147749</v>
+        <v>1.677090130540496</v>
       </c>
       <c r="G78">
-        <v>-11.35701124998348</v>
+        <v>-10.34449400744579</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-20.0609838895696</v>
       </c>
       <c r="E79">
-        <v>-11.38618519737669</v>
+        <v>-14.36704879548925</v>
       </c>
       <c r="F79">
-        <v>1.468873356907618</v>
+        <v>1.867261748670789</v>
       </c>
       <c r="G79">
-        <v>-11.00475392528293</v>
+        <v>-10.2596474189792</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-19.87409146120305</v>
       </c>
       <c r="E80">
-        <v>-13.85828040819776</v>
+        <v>-15.34974428026826</v>
       </c>
       <c r="F80">
-        <v>1.946859572405794</v>
+        <v>1.987916774358149</v>
       </c>
       <c r="G80">
-        <v>-12.47360452027361</v>
+        <v>-10.50141281109465</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-19.67908973017423</v>
       </c>
       <c r="E81">
-        <v>-13.84522271179249</v>
+        <v>-16.9051302278392</v>
       </c>
       <c r="F81">
-        <v>1.842158902896353</v>
+        <v>1.847506842848827</v>
       </c>
       <c r="G81">
-        <v>-10.48132835295522</v>
+        <v>-9.672485738948639</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-19.46443993798574</v>
       </c>
       <c r="E82">
-        <v>-13.843349613485</v>
+        <v>-16.73690440312702</v>
       </c>
       <c r="F82">
-        <v>1.755914259121286</v>
+        <v>1.845069785949791</v>
       </c>
       <c r="G82">
-        <v>-10.87802316134111</v>
+        <v>-9.727599862639336</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-19.22862402932284</v>
       </c>
       <c r="E83">
-        <v>-15.69549496984891</v>
+        <v>-18.13467182770939</v>
       </c>
       <c r="F83">
-        <v>1.023238201958373</v>
+        <v>1.489148477458538</v>
       </c>
       <c r="G83">
-        <v>-10.42248478061612</v>
+        <v>-9.912112931243971</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-18.97561775467018</v>
       </c>
       <c r="E84">
-        <v>-18.45315668494254</v>
+        <v>-18.52218721037251</v>
       </c>
       <c r="F84">
-        <v>0.8162888304517782</v>
+        <v>1.420031158103753</v>
       </c>
       <c r="G84">
-        <v>-10.21491753189965</v>
+        <v>-8.505271436409119</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-18.70350863101341</v>
       </c>
       <c r="E85">
-        <v>-18.71027369164003</v>
+        <v>-19.32397296305331</v>
       </c>
       <c r="F85">
-        <v>0.8406908774034461</v>
+        <v>1.660933652716294</v>
       </c>
       <c r="G85">
-        <v>-10.07419709306635</v>
+        <v>-8.609786069252863</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-18.42557958054488</v>
       </c>
       <c r="E86">
-        <v>-17.45050501974773</v>
+        <v>-19.86719223828426</v>
       </c>
       <c r="F86">
-        <v>0.8995115899414334</v>
+        <v>1.46343263980603</v>
       </c>
       <c r="G86">
-        <v>-9.621268151560178</v>
+        <v>-8.660331389909111</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-18.14573419497113</v>
       </c>
       <c r="E87">
-        <v>-20.74235277544081</v>
+        <v>-21.68044277059116</v>
       </c>
       <c r="F87">
-        <v>0.9389435350494955</v>
+        <v>1.309866577205447</v>
       </c>
       <c r="G87">
-        <v>-9.121493314483361</v>
+        <v>-8.470652963130958</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.87781770553374</v>
       </c>
       <c r="E88">
-        <v>-21.73711749232977</v>
+        <v>-21.85874428597737</v>
       </c>
       <c r="F88">
-        <v>1.030121935075637</v>
+        <v>1.076444240240185</v>
       </c>
       <c r="G88">
-        <v>-9.47103415943686</v>
+        <v>-8.058764926597084</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.63368460459929</v>
       </c>
       <c r="E89">
-        <v>-21.911992608373</v>
+        <v>-22.57518985235559</v>
       </c>
       <c r="F89">
-        <v>1.1180812993745</v>
+        <v>1.203471067989878</v>
       </c>
       <c r="G89">
-        <v>-8.826026211501002</v>
+        <v>-7.835508408260326</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.42123044340754</v>
       </c>
       <c r="E90">
-        <v>-23.94138041123529</v>
+        <v>-24.66140189256419</v>
       </c>
       <c r="F90">
-        <v>0.654272591975237</v>
+        <v>1.012199377948667</v>
       </c>
       <c r="G90">
-        <v>-8.343518839149809</v>
+        <v>-7.317964843496393</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.25650083068851</v>
       </c>
       <c r="E91">
-        <v>-25.62684493749986</v>
+        <v>-26.63939370528173</v>
       </c>
       <c r="F91">
-        <v>1.071046598243544</v>
+        <v>0.9948881559649628</v>
       </c>
       <c r="G91">
-        <v>-8.316831807939449</v>
+        <v>-7.405879056857541</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.13889612578266</v>
       </c>
       <c r="E92">
-        <v>-26.48198284285941</v>
+        <v>-28.59960354371202</v>
       </c>
       <c r="F92">
-        <v>0.4211807736036925</v>
+        <v>1.10708886393935</v>
       </c>
       <c r="G92">
-        <v>-8.804452323572338</v>
+        <v>-6.846333833111778</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.07242626887759</v>
       </c>
       <c r="E93">
-        <v>-28.40401843939754</v>
+        <v>-29.81705514541564</v>
       </c>
       <c r="F93">
-        <v>1.514648939586318</v>
+        <v>0.7172376266294301</v>
       </c>
       <c r="G93">
-        <v>-9.076777786499068</v>
+        <v>-7.487986974248055</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.04561718110445</v>
       </c>
       <c r="E94">
-        <v>-30.29723490255268</v>
+        <v>-31.56945074878548</v>
       </c>
       <c r="F94">
-        <v>0.3722731337750069</v>
+        <v>1.023322695433459</v>
       </c>
       <c r="G94">
-        <v>-8.68890468408655</v>
+        <v>-7.309735776545204</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.0490385886415</v>
       </c>
       <c r="E95">
-        <v>-31.5950137644898</v>
+        <v>-33.62961384756476</v>
       </c>
       <c r="F95">
-        <v>0.8127964334815756</v>
+        <v>0.6308281377412054</v>
       </c>
       <c r="G95">
-        <v>-9.68581750620316</v>
+        <v>-7.377521149108869</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.0701406652344</v>
       </c>
       <c r="E96">
-        <v>-36.71808092128664</v>
+        <v>-35.81234236575104</v>
       </c>
       <c r="F96">
-        <v>0.6954424518943724</v>
+        <v>0.829478096239152</v>
       </c>
       <c r="G96">
-        <v>-7.716145165554627</v>
+        <v>-7.532502780271127</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.08561827032078</v>
       </c>
       <c r="E97">
-        <v>-38.1345897119723</v>
+        <v>-38.07549366803131</v>
       </c>
       <c r="F97">
-        <v>0.1535062729000742</v>
+        <v>0.3779938390587402</v>
       </c>
       <c r="G97">
-        <v>-7.862846820246169</v>
+        <v>-8.161808404863734</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-17.08493128182875</v>
       </c>
       <c r="E98">
-        <v>-39.09923949354493</v>
+        <v>-39.48581625044864</v>
       </c>
       <c r="F98">
-        <v>0.5803366594383671</v>
+        <v>-0.01712084472856793</v>
       </c>
       <c r="G98">
-        <v>-9.805097205081942</v>
+        <v>-8.469151784991068</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-17.04656375582013</v>
       </c>
       <c r="E99">
-        <v>-42.88381178118168</v>
+        <v>-41.53613416178241</v>
       </c>
       <c r="F99">
-        <v>0.2251269185461195</v>
+        <v>0.1356988588420933</v>
       </c>
       <c r="G99">
-        <v>-10.09729435046393</v>
+        <v>-8.108387349040374</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.9683795348218</v>
       </c>
       <c r="E100">
-        <v>-42.85470192300596</v>
+        <v>-44.92388579678276</v>
       </c>
       <c r="F100">
-        <v>0.1855251581204835</v>
+        <v>-0.1976908562930126</v>
       </c>
       <c r="G100">
-        <v>-8.693682346688288</v>
+        <v>-8.317231251861889</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.84508588063949</v>
       </c>
       <c r="E101">
-        <v>-45.02698719131597</v>
+        <v>-46.21001593925658</v>
       </c>
       <c r="F101">
-        <v>-0.173924167139292</v>
+        <v>-0.4736175530633195</v>
       </c>
       <c r="G101">
-        <v>-9.382088701962221</v>
+        <v>-8.287477901129268</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.69375842219952</v>
       </c>
       <c r="E102">
-        <v>-49.89663992931141</v>
+        <v>-48.15395349571619</v>
       </c>
       <c r="F102">
-        <v>-0.7801143204665394</v>
+        <v>-0.5682610139353714</v>
       </c>
       <c r="G102">
-        <v>-9.639432407052849</v>
+        <v>-8.760751069861692</v>
       </c>
     </row>
   </sheetData>
